--- a/E2E_Functional_Test_Report.xlsx
+++ b/E2E_Functional_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="441">
   <si>
     <t>STREETSENTINEL — E2E FUNCTIONAL TEST AUDIT REPORT</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Test Execution Date</t>
   </si>
   <si>
-    <t>13/06/2026</t>
+    <t>6/13/2026</t>
   </si>
   <si>
     <t>Automation Tool</t>
@@ -149,6 +149,12 @@
     <t>Roles selection cards are loaded in view.</t>
   </si>
   <si>
+    <t>Failed in automation: Citizen role option not found on page.</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
     <t>Verify Citizen Role Selection Option</t>
   </si>
   <si>
@@ -194,6 +200,10 @@
     <t>All inputs and button are located in login form.</t>
   </si>
   <si>
+    <t xml:space="preserve">Failed in automation: Waiting for element to be located By(css selector, input[type="email"])
+Wait timed out after 5133ms</t>
+  </si>
+  <si>
     <t>Login Form Validation (Empty Fields)</t>
   </si>
   <si>
@@ -203,6 +213,10 @@
     <t>Validation warning "Please enter email and password" displays.</t>
   </si>
   <si>
+    <t xml:space="preserve">Failed in automation: no such element: Unable to locate element: {"method":"css selector","selector":"button[type="submit"]"}
+  (Session info: chrome=149.0.7827.53)</t>
+  </si>
+  <si>
     <t>Login Validation (Malformed Email)</t>
   </si>
   <si>
@@ -236,11 +250,8 @@
     <t>Access granted, user details retrieved, and redirects to dashboard.</t>
   </si>
   <si>
-    <t xml:space="preserve">Failed in automation: Waiting for URL to contain "/citizen/home"
-Wait timed out after 12026ms</t>
-  </si>
-  <si>
-    <t>FAIL</t>
+    <t xml:space="preserve">Failed in automation: no such element: Unable to locate element: {"method":"css selector","selector":"input[type="email"]"}
+  (Session info: chrome=149.0.7827.53)</t>
   </si>
   <si>
     <t>Firebase ID Token Retrieval</t>
@@ -295,7 +306,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //button[contains(@class, 'rounded-xl')])
-Wait timed out after 5206ms</t>
+Wait timed out after 5120ms</t>
   </si>
   <si>
     <t>Citizen Dashboard</t>
@@ -311,7 +322,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //*[contains(text(), 'STREET SENTINEL')])
-Wait timed out after 8075ms</t>
+Wait timed out after 8200ms</t>
   </si>
   <si>
     <t>Medium</t>
@@ -684,7 +695,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //*[contains(text(), 'Guardian Circle') or contains(text(), 'Contacts')])
-Wait timed out after 8204ms</t>
+Wait timed out after 8190ms</t>
   </si>
   <si>
     <t>Guardian Count Header</t>
@@ -757,7 +768,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: no such element: Unable to locate element: {"method":"xpath","selector":"//button[@title='Add New Contact']"}
-  (Session info: chrome=148.0.7778.179)</t>
+  (Session info: chrome=149.0.7827.53)</t>
   </si>
   <si>
     <t>Edit Contact Form Population</t>
@@ -1112,7 +1123,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //*[contains(text(), 'Voice Monitoring') or contains(text(), 'Settings')])
-Wait timed out after 8047ms</t>
+Wait timed out after 8186ms</t>
   </si>
   <si>
     <t>Voice Monitoring Switch Toggle</t>
@@ -1941,7 +1952,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="4">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1949,7 +1960,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -2100,10 +2111,10 @@
         <v>44</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>40</v>
+        <v>45</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>41</v>
@@ -2117,16 +2128,16 @@
         <v>35</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>40</v>
@@ -2143,16 +2154,16 @@
         <v>35</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>40</v>
@@ -2169,16 +2180,16 @@
         <v>35</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>40</v>
@@ -2195,19 +2206,19 @@
         <v>35</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>40</v>
+        <v>62</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>41</v>
@@ -2221,19 +2232,19 @@
         <v>35</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>40</v>
+        <v>66</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>41</v>
@@ -2247,16 +2258,16 @@
         <v>35</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>40</v>
@@ -2273,16 +2284,16 @@
         <v>35</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>40</v>
@@ -2299,19 +2310,19 @@
         <v>35</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>41</v>
@@ -2325,16 +2336,16 @@
         <v>35</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>40</v>
@@ -2351,16 +2362,16 @@
         <v>35</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>40</v>
@@ -2377,16 +2388,16 @@
         <v>35</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="F14" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>40</v>
@@ -2403,16 +2414,16 @@
         <v>35</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>40</v>
@@ -2429,19 +2440,19 @@
         <v>35</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>41</v>
@@ -2452,25 +2463,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2478,25 +2489,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E18" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>102</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2504,25 +2515,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2530,25 +2541,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2556,25 +2567,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2582,25 +2593,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2608,25 +2619,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2634,25 +2645,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2660,25 +2671,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2686,25 +2697,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2712,25 +2723,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2738,25 +2749,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2764,25 +2775,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2790,19 +2801,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>40</v>
@@ -2816,25 +2827,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2842,19 +2853,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>40</v>
@@ -2868,19 +2879,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>40</v>
@@ -2894,25 +2905,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2920,25 +2931,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H35" s="14" t="s">
         <v>172</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="36" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2946,19 +2957,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>40</v>
@@ -2972,25 +2983,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2998,25 +3009,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3024,25 +3035,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3050,25 +3061,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3076,19 +3087,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>40</v>
@@ -3102,25 +3113,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3128,25 +3139,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3154,25 +3165,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3180,25 +3191,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3206,25 +3217,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3232,25 +3243,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3258,25 +3269,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3284,25 +3295,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3310,25 +3321,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3336,25 +3347,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3362,25 +3373,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3388,25 +3399,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3414,25 +3425,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3440,25 +3451,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3466,25 +3477,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3492,25 +3503,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3518,25 +3529,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G58" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3544,25 +3555,25 @@
         <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3570,25 +3581,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3596,25 +3607,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3622,25 +3633,25 @@
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3648,25 +3659,25 @@
         <v>62</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3674,25 +3685,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3700,25 +3711,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3726,25 +3737,25 @@
         <v>65</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3752,25 +3763,25 @@
         <v>66</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3778,25 +3789,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3804,25 +3815,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3830,25 +3841,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3856,25 +3867,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3882,25 +3893,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="73" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3908,25 +3919,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H73" s="15" t="s">
         <v>328</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="74" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3934,25 +3945,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3960,25 +3971,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G75" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3986,25 +3997,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D76" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="E76" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="E76" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="F76" s="9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G76" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="77" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4012,25 +4023,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H77" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="78" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4038,25 +4049,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="79" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4064,25 +4075,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="80" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4090,25 +4101,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="81" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4116,25 +4127,25 @@
         <v>80</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H81" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="82" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4142,25 +4153,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="83" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4168,25 +4179,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="84" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4194,25 +4205,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D84" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E84" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="E84" s="9" t="s">
-        <v>367</v>
-      </c>
       <c r="F84" s="9" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="85" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4220,25 +4231,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H85" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4246,25 +4257,25 @@
         <v>85</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="87" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4272,25 +4283,25 @@
         <v>86</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="88" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4298,25 +4309,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="89" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4324,25 +4335,25 @@
         <v>88</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="90" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4350,25 +4361,25 @@
         <v>89</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4376,25 +4387,25 @@
         <v>90</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="92" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4402,25 +4413,25 @@
         <v>91</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H92" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4428,25 +4439,25 @@
         <v>92</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H93" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4454,25 +4465,25 @@
         <v>93</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4480,25 +4491,25 @@
         <v>94</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G95" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H95" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4506,25 +4517,25 @@
         <v>95</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G96" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H96" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4532,19 +4543,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G97" s="10" t="s">
         <v>40</v>
@@ -4558,19 +4569,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>40</v>
@@ -4584,25 +4595,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G99" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H99" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4610,25 +4621,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H100" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" ht="35" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4636,25 +4647,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H101" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/E2E_Functional_Test_Report.xlsx
+++ b/E2E_Functional_Test_Report.xlsx
@@ -32,7 +32,7 @@
     <t>Test Execution Date</t>
   </si>
   <si>
-    <t>6/13/2026</t>
+    <t>6/17/2026</t>
   </si>
   <si>
     <t>Automation Tool</t>
@@ -201,7 +201,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(css selector, input[type="email"])
-Wait timed out after 5133ms</t>
+Wait timed out after 5160ms</t>
   </si>
   <si>
     <t>Login Form Validation (Empty Fields)</t>
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: no such element: Unable to locate element: {"method":"css selector","selector":"button[type="submit"]"}
-  (Session info: chrome=149.0.7827.53)</t>
+  (Session info: chrome=149.0.7827.114)</t>
   </si>
   <si>
     <t>Login Validation (Malformed Email)</t>
@@ -251,7 +251,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: no such element: Unable to locate element: {"method":"css selector","selector":"input[type="email"]"}
-  (Session info: chrome=149.0.7827.53)</t>
+  (Session info: chrome=149.0.7827.114)</t>
   </si>
   <si>
     <t>Firebase ID Token Retrieval</t>
@@ -306,7 +306,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //button[contains(@class, 'rounded-xl')])
-Wait timed out after 5120ms</t>
+Wait timed out after 5145ms</t>
   </si>
   <si>
     <t>Citizen Dashboard</t>
@@ -322,7 +322,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //*[contains(text(), 'STREET SENTINEL')])
-Wait timed out after 8200ms</t>
+Wait timed out after 8072ms</t>
   </si>
   <si>
     <t>Medium</t>
@@ -695,7 +695,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //*[contains(text(), 'Guardian Circle') or contains(text(), 'Contacts')])
-Wait timed out after 8190ms</t>
+Wait timed out after 8021ms</t>
   </si>
   <si>
     <t>Guardian Count Header</t>
@@ -768,7 +768,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: no such element: Unable to locate element: {"method":"xpath","selector":"//button[@title='Add New Contact']"}
-  (Session info: chrome=149.0.7827.53)</t>
+  (Session info: chrome=149.0.7827.114)</t>
   </si>
   <si>
     <t>Edit Contact Form Population</t>
@@ -1123,7 +1123,7 @@
   </si>
   <si>
     <t xml:space="preserve">Failed in automation: Waiting for element to be located By(xpath, //*[contains(text(), 'Voice Monitoring') or contains(text(), 'Settings')])
-Wait timed out after 8186ms</t>
+Wait timed out after 8087ms</t>
   </si>
   <si>
     <t>Voice Monitoring Switch Toggle</t>

--- a/E2E_Functional_Test_Report.xlsx
+++ b/E2E_Functional_Test_Report.xlsx
@@ -32,7 +32,7 @@
     <t>Test Execution Date</t>
   </si>
   <si>
-    <t>18/06/2026</t>
+    <t>6/18/2026</t>
   </si>
   <si>
     <t>Automation Tool</t>

--- a/E2E_Functional_Test_Report.xlsx
+++ b/E2E_Functional_Test_Report.xlsx
@@ -32,7 +32,7 @@
     <t>Test Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026</t>
+    <t>6/22/2026</t>
   </si>
   <si>
     <t>Automation Tool</t>
